--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_time_of_day/lang_time_of_day__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_time_of_day/lang_time_of_day__ui__part_0001.xlsx
@@ -1,156 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="37">
-  <si>
-    <t>split_id</t>
-  </si>
-  <si>
-    <t>prompt_domain</t>
-  </si>
-  <si>
-    <t>prompt_file</t>
-  </si>
-  <si>
-    <t>source_file</t>
-  </si>
-  <si>
-    <t>original_index</t>
-  </si>
-  <si>
-    <t>database</t>
-  </si>
-  <si>
-    <t>table</t>
-  </si>
-  <si>
-    <t>primary_key_column</t>
-  </si>
-  <si>
-    <t>primary_key</t>
-  </si>
-  <si>
-    <t>column</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>source_en</t>
-  </si>
-  <si>
-    <t>new_translation_vi</t>
-  </si>
-  <si>
-    <t>translator_note</t>
-  </si>
-  <si>
-    <t>UI_0013680</t>
-  </si>
-  <si>
-    <t>UI_0013681</t>
-  </si>
-  <si>
-    <t>UI_0013682</t>
-  </si>
-  <si>
-    <t>UI_0013683</t>
-  </si>
-  <si>
-    <t>ui</t>
-  </si>
-  <si>
-    <t>ui_prompt.md</t>
-  </si>
-  <si>
-    <t>lang_time_of_day.json</t>
-  </si>
-  <si>
-    <t>lang_time_of_day.db</t>
-  </si>
-  <si>
-    <t>DaySelectPreset</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>general</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>Next Day</t>
-  </si>
-  <si>
-    <t>2 Days Later</t>
-  </si>
-  <si>
-    <t>3 Days Later</t>
-  </si>
-  <si>
-    <t>Ngày tiếp theo</t>
-  </si>
-  <si>
-    <t>2 ngày sau</t>
-  </si>
-  <si>
-    <t>3 ngày sau</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -184,16 +69,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -481,216 +433,344 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>split_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>prompt_domain</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>prompt_file</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>original_index</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>primary_key_column</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>primary_key</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>source_en</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>new_translation_vi</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>translator_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UI_0013680</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ui</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ui_prompt.md</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>lang_time_of_day.json</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>lang_time_of_day.db</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DaySelectPreset</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Mặc định</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UI_0013681</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ui</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ui_prompt.md</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>lang_time_of_day.json</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>lang_time_of_day.db</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DaySelectPreset</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Next Day</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Ngày tiếp theo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UI_0013682</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ui</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ui_prompt.md</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>lang_time_of_day.json</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>lang_time_of_day.db</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DaySelectPreset</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2 Days Later</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2 Ngày Sau</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UI_0013683</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ui</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ui_prompt.md</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>lang_time_of_day.json</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" t="s">
-        <v>36</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>lang_time_of_day.db</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DaySelectPreset</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3 Days Later</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3 Ngày Sau</t>
+        </is>
       </c>
     </row>
   </sheetData>
